--- a/benchmarks/attachment_intelligence/fixtures/files/f54.xlsx
+++ b/benchmarks/attachment_intelligence/fixtures/files/f54.xlsx
@@ -75,7 +75,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Новая цена, руб.</t>
+          <t xml:space="preserve">Новая цена</t>
         </is>
       </c>
     </row>
